--- a/artfynd/A 18510-2021 artfynd.xlsx
+++ b/artfynd/A 18510-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18510-2021 artfynd.xlsx
+++ b/artfynd/A 18510-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,130 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122295250</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99462</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>345</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sötgräs</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cinna latifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Trevir.) Griseb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jällvik, V om ån, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>622665</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6949024</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Y-Tim-0319</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-11-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-11-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elisabeth Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18510-2021 artfynd.xlsx
+++ b/artfynd/A 18510-2021 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>122295250</v>
       </c>
       <c r="B4" t="n">
-        <v>99478</v>
+        <v>99488</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2021 artfynd.xlsx
+++ b/artfynd/A 18510-2021 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>122295250</v>
       </c>
       <c r="B4" t="n">
-        <v>99488</v>
+        <v>99500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2021 artfynd.xlsx
+++ b/artfynd/A 18510-2021 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>122295250</v>
       </c>
       <c r="B4" t="n">
-        <v>99500</v>
+        <v>99505</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2021 artfynd.xlsx
+++ b/artfynd/A 18510-2021 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>122295250</v>
       </c>
       <c r="B4" t="n">
-        <v>99505</v>
+        <v>99514</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,11 +941,6 @@
       </c>
       <c r="E4" t="n">
         <v>345</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sötgräs</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2021 artfynd.xlsx
+++ b/artfynd/A 18510-2021 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>122295250</v>
       </c>
       <c r="B4" t="n">
-        <v>99514</v>
+        <v>99527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,6 +941,11 @@
       </c>
       <c r="E4" t="n">
         <v>345</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sötgräs</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2021 artfynd.xlsx
+++ b/artfynd/A 18510-2021 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>122295250</v>
       </c>
       <c r="B4" t="n">
-        <v>99527</v>
+        <v>99540</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2021 artfynd.xlsx
+++ b/artfynd/A 18510-2021 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>122295250</v>
       </c>
       <c r="B4" t="n">
-        <v>99540</v>
+        <v>99543</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2021 artfynd.xlsx
+++ b/artfynd/A 18510-2021 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>122295250</v>
       </c>
       <c r="B4" t="n">
-        <v>99543</v>
+        <v>99544</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 18510-2021 artfynd.xlsx
+++ b/artfynd/A 18510-2021 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>122295250</v>
       </c>
       <c r="B4" t="n">
-        <v>99544</v>
+        <v>99547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Y-Tim-0319</t>
+          <t>Y-Tim-0136</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">

--- a/artfynd/A 18510-2021 artfynd.xlsx
+++ b/artfynd/A 18510-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,130 +921,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>122295250</v>
-      </c>
-      <c r="B4" t="n">
-        <v>99547</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>345</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sötgräs</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Cinna latifolia</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Trevir.) Griseb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Jällvik, V om ån, Mpd</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>622665</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6949024</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Timrå</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Ljustorp</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Y-Tim-0136</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2012-11-03</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2012-11-03</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Elisabeth Nilsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
